--- a/artfynd/A 34310-2022 artfynd.xlsx
+++ b/artfynd/A 34310-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34310-2022 artfynd.xlsx
+++ b/artfynd/A 34310-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>399942</v>
       </c>
       <c r="B2" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592826.3955744901</v>
+        <v>592826</v>
       </c>
       <c r="R2" t="n">
-        <v>6527777.6988176</v>
+        <v>6527778</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2008-04-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,53 +791,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3421649</v>
+        <v>17312391</v>
       </c>
       <c r="B3" t="n">
-        <v>103264</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottorp 300 m ssv, Srm</t>
+          <t>300m SSV Ottorp, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592826.3955744901</v>
+        <v>592856</v>
       </c>
       <c r="R3" t="n">
-        <v>6527777.6988176</v>
+        <v>6527723</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,39 +882,39 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Ursula Zinko</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Ursula Zinko, Karl Ingvarson, Inger Holst</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17312391</v>
+        <v>17312392</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -958,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,14 +947,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>300m SSV Ottorp, Srm</t>
+          <t>250m S Ottorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592856.2062669551</v>
+        <v>592837</v>
       </c>
       <c r="R4" t="n">
-        <v>6527723.078194506</v>
+        <v>6527767</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,19 +984,9 @@
           <t>2015-03-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-03-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,19 +1023,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17312392</v>
+        <v>92051994</v>
       </c>
       <c r="B5" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1089,7 +1053,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,17 +1063,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>250m S Ottorp, Srm</t>
+          <t>Ottorp, 300 m SSV om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592837.0129398428</v>
+        <v>592859</v>
       </c>
       <c r="R5" t="n">
-        <v>6527767.093648813</v>
+        <v>6527717</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-03-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-03-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,44 +1114,34 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ursula Zinko</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Karl Ingvarson, Inger Holst</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92051997</v>
+        <v>92051995</v>
       </c>
       <c r="B6" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1220,7 +1164,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1230,14 +1174,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottorp, 250 m SSV om, Srm</t>
+          <t>Ottorp, 300 m SSV om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592859.8012770683</v>
+        <v>592839</v>
       </c>
       <c r="R6" t="n">
-        <v>6527745.92070227</v>
+        <v>6527756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,24 +1211,9 @@
           <t>2021-03-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>fyra ex i barrmattan under stor gran, två ex vidd stigen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,19 +1245,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92051995</v>
+        <v>92051997</v>
       </c>
       <c r="B7" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1351,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1361,14 +1285,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottorp, 300 m SSV om, Srm</t>
+          <t>Ottorp, 250 m SSV om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592839.3578587436</v>
+        <v>592860</v>
       </c>
       <c r="R7" t="n">
-        <v>6527755.77218618</v>
+        <v>6527746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1398,19 +1322,14 @@
           <t>2021-03-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-03-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>fyra ex i barrmattan under stor gran, två ex vidd stigen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,62 +1361,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>92051994</v>
+        <v>3421649</v>
       </c>
       <c r="B8" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottorp, 300 m SSV om, Srm</t>
+          <t>Ottorp 300 m ssv, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592858.9446503309</v>
+        <v>592826</v>
       </c>
       <c r="R8" t="n">
-        <v>6527716.937919356</v>
+        <v>6527778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1521,22 +1426,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,18 +1445,18 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 34310-2022 artfynd.xlsx
+++ b/artfynd/A 34310-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399942</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17312391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17312392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92051994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92051995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92051997</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,8 +1495,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3421649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>